--- a/output/pdf_financials_xlsx/CAG.xlsx
+++ b/output/pdf_financials_xlsx/CAG.xlsx
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.047286</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -15547,7 +15547,11 @@
           <t>Warrant Reserve (Note 6) ---</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -18180,7 +18184,11 @@
           <t>Translation reserve 43,786</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
         <v>0.047286</v>
       </c>
